--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_05-10-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_05-10-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{920D25E2-816C-4EAE-94AA-1FED0F30913F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFCD0C7-B65A-4A2E-A765-12332947608C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32250" yWindow="1245" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32490" yWindow="2835" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="271">
   <si>
     <t>SKU</t>
   </si>
@@ -830,6 +830,9 @@
   </si>
   <si>
     <t>£711.4</t>
+  </si>
+  <si>
+    <t>Insulation Superstore</t>
   </si>
 </sst>
 </file>
@@ -1216,8 +1219,8 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
-        <v>231</v>
+      <c r="F1" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -1273,7 +1276,7 @@
         <v>65</v>
       </c>
       <c r="F2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G2" t="s">
         <v>88</v>
@@ -1329,7 +1332,7 @@
         <v>66</v>
       </c>
       <c r="F3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G3" t="s">
         <v>89</v>
@@ -1385,7 +1388,7 @@
         <v>87</v>
       </c>
       <c r="F4" t="s">
-        <v>91</v>
+        <v>233</v>
       </c>
       <c r="G4" t="s">
         <v>90</v>
@@ -1441,7 +1444,7 @@
         <v>68</v>
       </c>
       <c r="F5" t="s">
-        <v>234</v>
+        <v>91</v>
       </c>
       <c r="G5" t="s">
         <v>91</v>
@@ -1497,7 +1500,7 @@
         <v>69</v>
       </c>
       <c r="F6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G6" t="s">
         <v>92</v>
@@ -1609,7 +1612,7 @@
         <v>71</v>
       </c>
       <c r="F8" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G8" t="s">
         <v>94</v>
@@ -1665,7 +1668,7 @@
         <v>72</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>236</v>
       </c>
       <c r="G9" t="s">
         <v>95</v>
@@ -1721,7 +1724,7 @@
         <v>73</v>
       </c>
       <c r="F10" t="s">
-        <v>237</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s">
         <v>96</v>
@@ -1777,7 +1780,7 @@
         <v>74</v>
       </c>
       <c r="F11" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G11" t="s">
         <v>97</v>
@@ -1833,7 +1836,7 @@
         <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G12" t="s">
         <v>98</v>
@@ -1889,7 +1892,7 @@
         <v>76</v>
       </c>
       <c r="F13" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G13" t="s">
         <v>99</v>
@@ -1945,7 +1948,7 @@
         <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G14" t="s">
         <v>100</v>
@@ -2001,7 +2004,7 @@
         <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G15" t="s">
         <v>101</v>
@@ -2057,7 +2060,7 @@
         <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>87</v>
+        <v>242</v>
       </c>
       <c r="G16" t="s">
         <v>102</v>
